--- a/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7481.05</v>
+        <v>7417.69</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3206.16</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26718.04</v>
+        <v>26438.24</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3497.93</v>
+        <v>3461.29</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17740.78</v>
+        <v>17554.99</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3398.53</v>
+        <v>3360.67</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4488.63</v>
+        <v>4464.05</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5639.91</v>
+        <v>5609.02</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3344.45</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3344.45</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7481.05</v>
+        <v>7507.75</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2229.63</v>
+        <v>2237.59</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5343.61</v>
+        <v>5401.73</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5343.61</v>
+        <v>5382.13</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4274.89</v>
+        <v>4305.71</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3198.15</v>
+        <v>3192.48</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3206.16</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3206.16</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="24">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5038-66-CM25</t>
+          <t>1746-281-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3206.16</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1746-281-CM25</t>
+          <t>5038-66-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2244.32</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7053.56</v>
+        <v>7089.99</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2707.71</v>
+        <v>2721.7</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9510.98</v>
+        <v>9560.1</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2351.19</v>
+        <v>2363.33</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5457.54</v>
+        <v>5437.97</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="33">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7640.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>828-67-CM25</t>
+          <t>4644-194-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2292.17</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="35">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16372.63</v>
+        <v>16183.15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4644-194-CM25</t>
+          <t>828-67-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2728.77</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5457.54</v>
+        <v>5411.31</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4366.04</v>
+        <v>4385.82</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5566.7</v>
+        <v>5591.92</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2837.92</v>
+        <v>2850.78</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4582.66</v>
+        <v>4594.81</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2281.25</v>
+        <v>2287.3</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3274.53</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3078.05</v>
+        <v>3099.24</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>13906.91</v>
+        <v>14002.64</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5457.54</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2281.25</v>
+        <v>2300.75</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10915.09</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12817.04</v>
+        <v>12974.56</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3274.53</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8568.34</v>
+        <v>8615.200000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>54575.44</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7094.81</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2375.66</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5656.33</v>
+        <v>5524.01</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>12202.96</v>
+        <v>11917.49</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6787.59</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5656.33</v>
+        <v>5656.36</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2375.66</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>33937.97</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>28281.64</v>
+        <v>28184.58</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5656.33</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6787.59</v>
+        <v>6745.06</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4525.06</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2375.66</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5656.33</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3393.8</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2367.21</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="69">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2367.21</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1746-9-CM26</t>
+          <t>1758-3-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>60.901.013-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2375.66</v>
+        <v>3378.18</v>
       </c>
     </row>
     <row r="71">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2828.16</v>
+        <v>2912.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1758-3-CM26</t>
+          <t>1746-9-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.901.013-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3280.67</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5800.33</v>
+        <v>5779.68</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15080.86</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8120.46</v>
+        <v>8142.75</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>14712.07</v>
+        <v>14814.5</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5800.33</v>
+        <v>5838.53</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2424.54</v>
+        <v>2446.13</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4640.26</v>
+        <v>4635.48</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5568.32</v>
+        <v>5528.43</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5800.33</v>
+        <v>5758.78</v>
       </c>
     </row>
     <row r="82">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5800.33</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2182-19-CM26</t>
+          <t>1195-87-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2427.47</v>
+        <v>2421.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1195-87-CM26</t>
+          <t>2182-19-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2436.14</v>
+        <v>2413.17</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2900.16</v>
+        <v>2915.18</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6594.18</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>32970.9</v>
+        <v>34426.96</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4875.3</v>
+        <v>5016.91</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11701.37</v>
+        <v>11618.8</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9451.66</v>
+        <v>9599.709999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2967.38</v>
+        <v>2967.23</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2637.67</v>
+        <v>2637.54</v>
       </c>
     </row>
     <row r="94">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7693.21</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3791-253-CM26</t>
+          <t>4778-65-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5045.86</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4778-65-CM26</t>
+          <t>3791-253-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>10990.3</v>
+        <v>5031.94</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2151-83-CM26</t>
+          <t>3797-218-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2304.3</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2151-84-CM26</t>
+          <t>2151-85-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2151-85-CM26</t>
+          <t>2151-84-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3797-218-CM26</t>
+          <t>2151-83-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>8792.24</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3297.09</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7693.21</v>
+        <v>7578.46</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="104">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2304.34</v>
+        <v>2291.1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5575-47-CM26</t>
+          <t>1403-189-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>27475.75</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5038-24-CM26</t>
+          <t>5038-23-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5495.15</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1403-189-CM26</t>
+          <t>5038-24-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2747.58</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5038-23-CM26</t>
+          <t>5575-47-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3297.09</v>
+        <v>27299.73</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2307.96</v>
+        <v>2298.02</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5495.15</v>
+        <v>5415.65</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8521.040000000001</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6682.36</v>
+        <v>6506.39</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3898.04</v>
+        <v>3909.39</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5568.63</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="115">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>27843.17</v>
+        <v>28079.48</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3791-358-CM26</t>
+          <t>1403-260-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5568.63</v>
+        <v>2779.66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1403-260-CM26</t>
+          <t>886182-114-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7549,17 +7549,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2784.32</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>886182-114-CM26</t>
+          <t>3791-358-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7610,17 +7610,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>7239.22</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3791-376-CM26</t>
+          <t>4852-6-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>7836.18</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4852-6-CM26</t>
+          <t>3791-376-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4454.91</v>
+        <v>7940.5</v>
       </c>
     </row>
     <row r="121">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2450.2</v>
+        <v>2496.54</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>854-60-CM26</t>
+          <t>3791-417-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5568.63</v>
+        <v>6742.56</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3791-417-CM26</t>
+          <t>854-60-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>6682.36</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11137.27</v>
+        <v>11208.5</v>
       </c>
     </row>
     <row r="125">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5568.63</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1746-91-CM26</t>
+          <t>4778-204-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2338.83</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2151-142-CM26</t>
+          <t>4144-95-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>817607-14-CM26</t>
+          <t>2151-141-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>18885.47</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4144-95-CM26</t>
+          <t>2151-142-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3341.18</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>4778-204-CM26</t>
+          <t>1746-91-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>11137.27</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2151-141-CM26</t>
+          <t>817607-14-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3341.18</v>
+        <v>18924.59</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11140.35</v>
+        <v>10988.89</v>
       </c>
     </row>
     <row r="133">
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7628.91</v>
+        <v>7669.99</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3540-277-CM26</t>
+          <t>868-63-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3119.3</v>
+        <v>24694.41</v>
       </c>
     </row>
     <row r="135">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>11140.35</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>868-63-CM26</t>
+          <t>3540-277-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>24508.77</v>
+        <v>3142.92</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2785.09</v>
+        <v>2795.64</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6684.21</v>
+        <v>6709.53</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2464.25</v>
+        <v>2487.66</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2450.88</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7628.91</v>
+        <v>7552.83</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5570.17</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="144">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4456.14</v>
+        <v>4446.03</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4778-260-CM26</t>
+          <t>1692-352-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>11140.35</v>
+        <v>3889.49</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1692-352-CM26</t>
+          <t>4778-260-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3899.12</v>
+        <v>11112.84</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3791-622-CM26</t>
+          <t>2713-587-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>6684.21</v>
+        <v>55879.03</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2713-587-CM26</t>
+          <t>3791-622-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>55701.75</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>6684.21</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3342.1</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>27673.72</v>
+        <v>28069.7</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3320.85</v>
+        <v>3359.8</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>49812.69</v>
+        <v>50319.25</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7332.43</v>
+        <v>7406.99</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11069.49</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11069.49</v>
+        <v>11119.76</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2656.68</v>
+        <v>2696.24</v>
       </c>
     </row>
     <row r="158">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5534.74</v>
+        <v>5639.97</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1403-454-CM26</t>
+          <t>3791-722-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3320.85</v>
+        <v>6972.59</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3791-722-CM26</t>
+          <t>1403-454-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>6818.8</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4427.79</v>
+        <v>4458.36</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>6641.69</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>33208.46</v>
+        <v>33120.63</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>14038.43</v>
+        <v>13851.44</v>
       </c>
     </row>
     <row r="165">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2452.21</v>
+        <v>2419.55</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4778-368-CM26</t>
+          <t>4778-356-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>11069.49</v>
+        <v>8139.61</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4778-356-CM26</t>
+          <t>4778-368-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8302.110000000001</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2374.6</v>
+        <v>2325.8</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10741.48</v>
+        <v>10843.52</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6616.75</v>
+        <v>6642.58</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5370.74</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3759.52</v>
+        <v>3778.68</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>10741.48</v>
+        <v>10783.3</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2309.42</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="175">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>7519.04</v>
+        <v>7535.06</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>527225-7-CM26</t>
+          <t>1113146-13-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2309.82</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1113144-27-CM26</t>
+          <t>527225-7-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3222.45</v>
+        <v>2315.11</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1113146-13-CM26</t>
+          <t>1113144-27-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5370.74</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5370.74</v>
+        <v>5406.69</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6444.89</v>
+        <v>6488.03</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5955.08</v>
+        <v>5996.76</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>14207.76</v>
+        <v>14179.28</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2309.42</v>
+        <v>2272.15</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3759.52</v>
+        <v>3699.24</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5370.74</v>
+        <v>5308.25</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5370.74</v>
+        <v>5340.97</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2308.85</v>
+        <v>2297.5</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3222.45</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5950.78</v>
+        <v>5990.61</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,251 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2857.23</v>
+        <v>2876.36</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>4778-442-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>16156.48</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2151-301-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>2352.08</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>3791-946-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>6065.79</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4609-400-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>10888.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M194"/>
+  <dimension ref="A1:M210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3797-2615-CM25</t>
+          <t>734-14-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7417.69</v>
+        <v>24694.77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1692-2931-CM25</t>
+          <t>1343644-16-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3189.69</v>
+        <v>17441.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5575-172-CM25</t>
+          <t>2500-48-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26438.24</v>
+        <v>6522.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1092-3291-CM25</t>
+          <t>2494-116-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3461.29</v>
+        <v>9475.379999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1092-3292-CM25</t>
+          <t>1692-2408-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>17554.99</v>
+        <v>2641.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3540-1128-CM25</t>
+          <t>734-433-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3360.67</v>
+        <v>26590.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>657-187-CM25</t>
+          <t>1403-3789-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4464.05</v>
+        <v>3083.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1113144-113-CM25</t>
+          <t>1692-2567-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5609.02</v>
+        <v>5325.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5038-60-CM25</t>
+          <t>3791-591-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3202.08</v>
+        <v>5374.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5038-61-CM25</t>
+          <t>697209-18-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3202.08</v>
+        <v>2218.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2151-390-CM25</t>
+          <t>4778-396-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3340.19</v>
+        <v>6264.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2151-391-CM25</t>
+          <t>2500-115-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3340.19</v>
+        <v>5174.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1233615-11764-CM25</t>
+          <t>1403-4049-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7507.75</v>
+        <v>6209.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1458-58-CM25</t>
+          <t>1233615-1323-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.103.003-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERPLAC XI Región</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2237.59</v>
+        <v>22312.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1256-10-CM25</t>
+          <t>4609-385-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.805.025-6</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2268.73</v>
+        <v>3098.05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3791-1228-CM25</t>
+          <t>2042-287-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.400-k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5401.73</v>
+        <v>5174.11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2500-169-CM25</t>
+          <t>3797-2615-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5382.13</v>
+        <v>7417.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1113146-69-CM25</t>
+          <t>1692-2931-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4305.71</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4889-188-CM25</t>
+          <t>1092-3292-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.620.850-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Aysen</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3192.48</v>
+        <v>17554.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>697209-44-CM25</t>
+          <t>1092-3291-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2235.06</v>
+        <v>3461.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2500-172-CM25</t>
+          <t>5575-172-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3192.95</v>
+        <v>26438.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>697209-43-CM25</t>
+          <t>3540-1128-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3192.95</v>
+        <v>3360.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3791-1290-CM25</t>
+          <t>1113144-113-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5335.33</v>
+        <v>5609.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1746-281-CM25</t>
+          <t>657-187-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2240.84</v>
+        <v>4464.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5038-66-CM25</t>
+          <t>2151-391-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3201.2</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1092-3310-CM25</t>
+          <t>2151-390-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7089.99</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>907-208-CM25</t>
+          <t>5038-61-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,22 +2115,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2721.7</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>907-209-CM25</t>
+          <t>5038-60-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>9560.1</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4649-284-CM25</t>
+          <t>1233615-11764-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2363.33</v>
+        <v>7507.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1233615-11987-CM25</t>
+          <t>1458-58-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.103.003-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERPLAC XI Región</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5437.97</v>
+        <v>2237.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4609-601-CM25</t>
+          <t>3791-1228-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7613.16</v>
+        <v>5401.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3797-5103-CM25</t>
+          <t>1256-10-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>60.805.025-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>Tesorería Regional de Aysén</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7613.16</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4644-194-CM25</t>
+          <t>1113146-69-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2697.19</v>
+        <v>4305.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3950-4873-CM25</t>
+          <t>2500-169-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16183.15</v>
+        <v>5382.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>828-67-CM25</t>
+          <t>4889-188-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.620.850-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Subsecretaria de las Culturas y las Artes Región de Aysen</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2265.64</v>
+        <v>3192.48</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>734-1194-CM25</t>
+          <t>697209-44-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>5411.31</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2500-179-CM25</t>
+          <t>697209-43-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,27 +2720,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>4385.82</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>697209-52-CM25</t>
+          <t>2500-172-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5591.92</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2713-1293-CM25</t>
+          <t>3791-1290-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2850.78</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>854-406-CM25</t>
+          <t>1746-281-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,27 +2903,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4594.81</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1692-3034-CM25</t>
+          <t>5038-66-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2287.3</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>548870-76-CM25</t>
+          <t>4649-284-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3283.21</v>
+        <v>2363.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5038-72-CM25</t>
+          <t>1092-3310-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3099.24</v>
+        <v>7089.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3797-5159-CM25</t>
+          <t>907-208-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14002.64</v>
+        <v>2721.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1403-4406-CM25</t>
+          <t>907-209-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5504.18</v>
+        <v>9560.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3949-472-CM25</t>
+          <t>3797-5103-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2300.75</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>907-227-CM25</t>
+          <t>1233615-11987-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11032.17</v>
+        <v>5437.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1428-82-CM25</t>
+          <t>4609-601-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>12974.56</v>
+        <v>7613.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2713-1333-CM25</t>
+          <t>4644-194-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3316.6</v>
+        <v>2697.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>657-238-CM25</t>
+          <t>3950-4873-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>8615.200000000001</v>
+        <v>16183.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1233615-12146-CM25</t>
+          <t>828-67-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>54873.9</v>
+        <v>2265.64</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1494998-7-CM25</t>
+          <t>734-1194-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7133.61</v>
+        <v>5411.31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3540-3-CM26</t>
+          <t>2713-1293-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2320.08</v>
+        <v>2850.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3791-1-CM26</t>
+          <t>2500-179-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5524.01</v>
+        <v>4385.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>817607-1-CM26</t>
+          <t>697209-52-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11917.49</v>
+        <v>5591.92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1343645-3-CM26</t>
+          <t>1692-3034-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6701.44</v>
+        <v>2287.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4778-704-CM25</t>
+          <t>548870-76-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5656.36</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1426103-9-CM26</t>
+          <t>854-406-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,27 +4001,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2378.96</v>
+        <v>4594.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2713-42-CM26</t>
+          <t>5038-72-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>33914.78</v>
+        <v>3099.24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>734-9-CM26</t>
+          <t>3797-5159-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>28184.58</v>
+        <v>14002.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>418-55-CM26</t>
+          <t>1403-4406-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5626.45</v>
+        <v>5504.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2500-4-CM26</t>
+          <t>3949-472-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6745.06</v>
+        <v>2300.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4778-17-CM26</t>
+          <t>907-227-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,27 +4306,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4586</v>
+        <v>11032.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3791-37-CM26</t>
+          <t>1428-82-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2407.65</v>
+        <v>12974.56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5038-13-CM26</t>
+          <t>2713-1333-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5793.88</v>
+        <v>3316.6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5038-14-CM26</t>
+          <t>1233615-12146-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,27 +4489,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3476.33</v>
+        <v>54873.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2151-19-CM26</t>
+          <t>657-238-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2438.99</v>
+        <v>8615.200000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2151-21-CM26</t>
+          <t>1494998-7-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2438.99</v>
+        <v>7133.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1758-3-CM26</t>
+          <t>3540-3-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.901.013-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3378.18</v>
+        <v>2320.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1692-36-CM26</t>
+          <t>3791-1-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2912.23</v>
+        <v>5524.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1746-9-CM26</t>
+          <t>817607-1-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,22 +4799,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2446.27</v>
+        <v>11917.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3791-69-CM26</t>
+          <t>1343645-3-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,27 +4855,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,28 +4900,28 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5779.68</v>
+        <v>6701.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5575-19-CM26</t>
+          <t>4778-704-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,28 +4961,28 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15017.27</v>
+        <v>5656.36</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4609-64-CM26</t>
+          <t>1426103-9-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,28 +5022,28 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8142.75</v>
+        <v>2378.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>907-18-CM26</t>
+          <t>2713-42-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,28 +5083,28 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>14814.5</v>
+        <v>33914.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2500-29-CM26</t>
+          <t>734-9-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,28 +5144,28 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5838.53</v>
+        <v>28184.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1428275-2-CM26</t>
+          <t>418-55-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,43 +5205,43 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2446.13</v>
+        <v>5626.45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1485465-9-CM26</t>
+          <t>2500-4-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,28 +5266,28 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4635.48</v>
+        <v>6745.06</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1195-80-CM26</t>
+          <t>4778-17-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,43 +5327,43 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>5528.43</v>
+        <v>4586</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2042-57-CM26</t>
+          <t>3791-37-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.253.400-k</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TORTEL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,43 +5388,43 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5758.78</v>
+        <v>2407.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3791-152-CM26</t>
+          <t>5038-13-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,43 +5449,43 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5768.74</v>
+        <v>5793.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1195-87-CM26</t>
+          <t>5038-14-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,43 +5510,43 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2421.78</v>
+        <v>3476.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2182-19-CM26</t>
+          <t>2151-19-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,28 +5571,28 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2413.17</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1332-8-CM26</t>
+          <t>2151-21-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,28 +5632,28 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2882.54</v>
+        <v>2438.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1608-21-CM26</t>
+          <t>1746-9-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,28 +5693,28 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2915.18</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>734-77-CM26</t>
+          <t>1758-3-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.901.013-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,28 +5754,28 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>6885.39</v>
+        <v>3378.18</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>734-78-CM26</t>
+          <t>1692-36-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,28 +5815,28 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>34426.96</v>
+        <v>2912.23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3791-177-CM26</t>
+          <t>3791-69-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2239-13-LR25</t>
+          <t>2239-3-LR24</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5016.91</v>
+        <v>5779.68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>817607-5-CM26</t>
+          <t>5575-19-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11618.8</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3765-241-CM26</t>
+          <t>4609-64-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9599.709999999999</v>
+        <v>8142.75</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>613-10-CM26</t>
+          <t>907-18-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,27 +6014,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.836.000-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2967.23</v>
+        <v>14814.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3540-166-CM26</t>
+          <t>2500-29-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2637.54</v>
+        <v>5838.53</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1686-4-CM26</t>
+          <t>1428275-2-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7699.84</v>
+        <v>2446.13</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4778-65-CM26</t>
+          <t>1485465-9-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,27 +6197,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>10959.99</v>
+        <v>4635.48</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3791-253-CM26</t>
+          <t>1195-80-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5031.94</v>
+        <v>5528.43</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3797-218-CM26</t>
+          <t>2042-57-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.253.400-k</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE TORTEL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8690.74</v>
+        <v>5758.78</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2151-85-CM26</t>
+          <t>3791-152-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2277.7</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2151-84-CM26</t>
+          <t>1195-87-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2277.7</v>
+        <v>2421.78</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2151-83-CM26</t>
+          <t>2182-19-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,27 +6502,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2277.7</v>
+        <v>2413.17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4609-124-CM26</t>
+          <t>1332-8-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>3247.91</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4609-125-CM26</t>
+          <t>1608-21-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7578.46</v>
+        <v>2915.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1746-39-CM26</t>
+          <t>734-78-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2273.54</v>
+        <v>34426.96</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1521-9-CM26</t>
+          <t>734-77-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.947.700-6</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Coyhaique</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2291.1</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1403-189-CM26</t>
+          <t>3791-177-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2729.97</v>
+        <v>5016.91</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>5038-23-CM26</t>
+          <t>817607-5-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3275.97</v>
+        <v>11618.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5038-24-CM26</t>
+          <t>3765-241-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5459.95</v>
+        <v>9599.709999999999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5575-47-CM26</t>
+          <t>613-10-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.836.000-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>27299.73</v>
+        <v>2967.23</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>907-41-CM26</t>
+          <t>3540-166-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2298.02</v>
+        <v>2637.54</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3791-274-CM26</t>
+          <t>1686-4-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>5415.65</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3791-316-CM26</t>
+          <t>4778-65-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8353</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2500-46-CM26</t>
+          <t>3791-253-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6506.39</v>
+        <v>5031.94</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1692-233-CM26</t>
+          <t>2151-83-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3909.39</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4144-86-CM26</t>
+          <t>2151-84-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7356,27 +7356,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5615.9</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>734-202-CM26</t>
+          <t>2151-85-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>28079.48</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1403-260-CM26</t>
+          <t>3797-218-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2779.66</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>886182-114-CM26</t>
+          <t>4609-125-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7539,27 +7539,27 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>7227.12</v>
+        <v>7578.46</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3791-358-CM26</t>
+          <t>1746-39-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5559.32</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>4852-6-CM26</t>
+          <t>4609-124-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4514.21</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3791-376-CM26</t>
+          <t>1521-9-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.947.700-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Departamento Provincial de Coyhaique</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>7940.5</v>
+        <v>2291.1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>548870-15-CM26</t>
+          <t>1403-189-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2496.54</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3791-417-CM26</t>
+          <t>5038-23-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,27 +7844,27 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>6742.56</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>854-60-CM26</t>
+          <t>5038-24-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7905,27 +7905,27 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5618.8</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3797-289-CM26</t>
+          <t>5575-47-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11208.5</v>
+        <v>27299.73</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5038-34-CM26</t>
+          <t>907-41-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5591.72</v>
+        <v>2298.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4778-204-CM26</t>
+          <t>3791-274-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>11160.34</v>
+        <v>5415.65</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4144-95-CM26</t>
+          <t>3791-316-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,22 +8154,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3348.1</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2151-141-CM26</t>
+          <t>2500-46-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3348.1</v>
+        <v>6506.39</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2151-142-CM26</t>
+          <t>1692-233-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3348.1</v>
+        <v>3909.39</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1746-91-CM26</t>
+          <t>734-202-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2343.67</v>
+        <v>28079.48</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>817607-14-CM26</t>
+          <t>4144-86-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,22 +8398,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>18924.59</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4609-178-CM26</t>
+          <t>3791-358-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>10988.89</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3791-501-CM26</t>
+          <t>1403-260-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7669.99</v>
+        <v>2779.66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>868-63-CM26</t>
+          <t>886182-114-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8576,27 +8576,27 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>24694.41</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2713-518-CM26</t>
+          <t>4852-6-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>11224.73</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>3540-277-CM26</t>
+          <t>3791-376-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3142.92</v>
+        <v>7940.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1608-45-CM26</t>
+          <t>548870-15-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2795.64</v>
+        <v>2496.54</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3791-525-CM26</t>
+          <t>854-60-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6709.53</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>3791-541-CM26</t>
+          <t>3791-417-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2487.66</v>
+        <v>6742.56</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>911089-31-CM26</t>
+          <t>3797-289-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8942,12 +8942,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.980.470-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Zona de Bienestar "Coyhaique"</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2469.14</v>
+        <v>11208.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3791-563-CM26</t>
+          <t>5038-34-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7552.83</v>
+        <v>5591.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2500-74-CM26</t>
+          <t>2151-142-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5545.76</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1426103-39-CM26</t>
+          <t>817607-14-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2754.79</v>
+        <v>18924.59</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1403-357-CM26</t>
+          <t>1746-91-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4446.03</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1692-352-CM26</t>
+          <t>2151-141-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3889.49</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4778-260-CM26</t>
+          <t>4144-95-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,27 +9308,27 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>11112.84</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2713-587-CM26</t>
+          <t>4778-204-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>55879.03</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3791-622-CM26</t>
+          <t>4609-178-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6705.48</v>
+        <v>10988.89</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2500-84-CM26</t>
+          <t>3791-501-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>6719.75</v>
+        <v>7669.99</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1746-127-CM26</t>
+          <t>3540-277-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3359.88</v>
+        <v>3142.92</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1195-285-CM26</t>
+          <t>2713-518-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>28069.7</v>
+        <v>11224.73</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>817607-23-CM26</t>
+          <t>868-63-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3359.8</v>
+        <v>24694.41</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1233615-887-CM26</t>
+          <t>1608-45-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>50319.25</v>
+        <v>2795.64</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3791-657-CM26</t>
+          <t>3791-525-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7406.99</v>
+        <v>6709.53</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1233615-913-CM26</t>
+          <t>3791-541-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10882.46</v>
+        <v>2487.66</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>707426-92-CM26</t>
+          <t>911089-31-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.470-8</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Zona de Bienestar "Coyhaique"</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>11119.76</v>
+        <v>2469.14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3540-366-CM26</t>
+          <t>3791-563-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2696.24</v>
+        <v>7552.83</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>817607-29-CM26</t>
+          <t>2500-74-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10040,12 +10040,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5639.97</v>
+        <v>5545.76</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3791-722-CM26</t>
+          <t>1426103-39-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6972.59</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1403-454-CM26</t>
+          <t>1403-357-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3395.74</v>
+        <v>4446.03</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1195-366-CM26</t>
+          <t>4778-260-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>4458.36</v>
+        <v>11112.84</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3791-730-CM26</t>
+          <t>1692-352-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>6687.55</v>
+        <v>3889.49</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>734-414-CM26</t>
+          <t>3791-622-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>33120.63</v>
+        <v>6705.48</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>907-93-CM26</t>
+          <t>2713-587-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>13851.44</v>
+        <v>55879.03</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>749-17-CM26</t>
+          <t>2500-84-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2419.55</v>
+        <v>6719.75</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4778-356-CM26</t>
+          <t>1746-127-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>8139.61</v>
+        <v>3359.88</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4778-368-CM26</t>
+          <t>1195-285-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>10852.81</v>
+        <v>28069.7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2493-58-CM26</t>
+          <t>817607-23-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2325.8</v>
+        <v>3359.8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4609-280-CM26</t>
+          <t>1233615-887-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10843.52</v>
+        <v>50319.25</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3791-775-CM26</t>
+          <t>3791-657-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6642.58</v>
+        <v>7406.99</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>418-2164-CM26</t>
+          <t>1233615-913-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>5424.76</v>
+        <v>10882.46</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1256-8-CM26</t>
+          <t>707426-92-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.805.025-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3778.68</v>
+        <v>11119.76</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1092-59-CM26</t>
+          <t>3540-366-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10955,12 +10955,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>10783.3</v>
+        <v>2696.24</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3797-488-CM26</t>
+          <t>817607-29-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2314.34</v>
+        <v>5639.97</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3797-489-CM26</t>
+          <t>1403-454-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>7535.06</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1113146-13-CM26</t>
+          <t>3791-722-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5383.06</v>
+        <v>6972.59</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>527225-7-CM26</t>
+          <t>1195-366-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2315.11</v>
+        <v>4458.36</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1113144-27-CM26</t>
+          <t>3791-730-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3229.84</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1692-461-CM26</t>
+          <t>734-414-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11321,27 +11321,27 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5406.69</v>
+        <v>33120.63</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>3791-826-CM26</t>
+          <t>907-93-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>6488.03</v>
+        <v>13851.44</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3791-830-CM26</t>
+          <t>749-17-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11443,27 +11443,27 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5996.76</v>
+        <v>2419.55</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>817607-35-CM26</t>
+          <t>4778-356-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11504,12 +11504,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>14179.28</v>
+        <v>8139.61</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3540-477-CM26</t>
+          <t>4778-368-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2272.15</v>
+        <v>10852.81</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1113146-22-CM26</t>
+          <t>2493-58-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11626,12 +11626,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3699.24</v>
+        <v>2325.8</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4649-69-CM26</t>
+          <t>4609-280-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5308.25</v>
+        <v>10843.52</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2500-114-CM26</t>
+          <t>3791-775-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5340.97</v>
+        <v>6642.58</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1415-34-CM26</t>
+          <t>418-2164-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>60.511.111-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2297.5</v>
+        <v>5424.76</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4609-321-CM26</t>
+          <t>1256-8-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.805.025-6</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>Tesorería Regional de Aysén</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3206.6</v>
+        <v>3778.68</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3791-884-CM26</t>
+          <t>1092-59-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,22 +11936,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5990.61</v>
+        <v>10783.3</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1286987-25-CM26</t>
+          <t>3797-488-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11997,22 +11997,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>65.797.310-6</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Coy</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2876.36</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4778-442-CM26</t>
+          <t>3797-489-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>16156.48</v>
+        <v>7535.06</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2151-301-CM26</t>
+          <t>1113146-13-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2352.08</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3791-946-CM26</t>
+          <t>527225-7-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12175,27 +12175,27 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6065.79</v>
+        <v>2315.11</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>4609-400-CM26</t>
+          <t>1113144-27-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12236,12 +12236,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12281,6 +12281,982 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
+        <v>3229.84</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1692-461-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>5406.69</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>3791-826-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>6488.03</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>3791-830-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>5996.76</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>817607-35-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>14179.28</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>3540-477-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.101.037-0</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>2272.15</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1113146-22-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>3699.24</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4649-69-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>5308.25</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2500-114-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>5340.97</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1415-34-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>60.511.111-4</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>2297.5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4609-321-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>3206.6</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>3791-884-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>5990.61</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1286987-25-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>65.797.310-6</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Deportes y Recreación Coy</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>2876.36</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4778-442-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>16156.48</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2151-301-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>2352.08</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>3791-946-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>6065.79</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>4609-400-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
         <v>10888.26</v>
       </c>
     </row>

--- a/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M412"/>
+  <dimension ref="A1:M431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3791-49-CM25</t>
+          <t>1403-29-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2095.95</v>
+        <v>4228.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1403-29-CM25</t>
+          <t>3791-49-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4228.12</v>
+        <v>2095.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2500-11-CM25</t>
+          <t>817607-12-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2543.36</v>
+        <v>3052.04</v>
       </c>
     </row>
     <row r="15">
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>817607-12-CM25</t>
+          <t>2500-11-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3052.04</v>
+        <v>2543.36</v>
       </c>
     </row>
     <row r="17">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1343644-16-CM25</t>
+          <t>817607-16-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE O HIGGINS</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17441.63</v>
+        <v>3039.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>817607-16-CM25</t>
+          <t>1343644-16-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3039.14</v>
+        <v>17441.63</v>
       </c>
     </row>
     <row r="23">
@@ -2789,7 +2789,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4889-15-CM25</t>
+          <t>418-644-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.620.850-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2164.82</v>
+        <v>5280.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>418-644-CM25</t>
+          <t>4889-15-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>65.620.850-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5280.05</v>
+        <v>2164.82</v>
       </c>
     </row>
     <row r="39">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1686-2-CM25</t>
+          <t>4778-94-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7467.06</v>
+        <v>5333.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4778-94-CM25</t>
+          <t>1686-2-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5333.62</v>
+        <v>7467.06</v>
       </c>
     </row>
     <row r="45">
@@ -3439,7 +3439,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3797-164-CM25</t>
+          <t>1746-42-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5415.24</v>
+        <v>2211.58</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1746-42-CM25</t>
+          <t>1113144-12-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3569,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1113144-12-CM25</t>
+          <t>3797-164-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2211.58</v>
+        <v>5415.24</v>
       </c>
     </row>
     <row r="50">
@@ -3699,7 +3699,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4645-5-CM25</t>
+          <t>4609-107-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3323.31</v>
+        <v>5448.05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4609-107-CM25</t>
+          <t>1092-36-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5448.05</v>
+        <v>6728.34</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1092-36-CM25</t>
+          <t>4645-5-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6728.34</v>
+        <v>3323.31</v>
       </c>
     </row>
     <row r="54">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2151-83-CM25</t>
+          <t>2151-84-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4154,7 +4154,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2151-84-CM25</t>
+          <t>2151-85-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4219,7 +4219,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2151-85-CM25</t>
+          <t>2151-83-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1234-9-CM25</t>
+          <t>4778-154-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.804.019-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3028.22</v>
+        <v>8075.26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4778-154-CM25</t>
+          <t>1234-9-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.804.019-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8075.26</v>
+        <v>3028.22</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2713-310-CM25</t>
+          <t>1113146-4-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>28627.22</v>
+        <v>7156.81</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1113146-4-CM25</t>
+          <t>2713-310-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7156.81</v>
+        <v>28627.22</v>
       </c>
     </row>
     <row r="68">
@@ -5324,7 +5324,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>734-433-CM25</t>
+          <t>3791-442-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26590.65</v>
+        <v>5318.13</v>
       </c>
     </row>
     <row r="77">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3791-442-CM25</t>
+          <t>734-433-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5318.13</v>
+        <v>26590.65</v>
       </c>
     </row>
     <row r="79">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4778-238-CM25</t>
+          <t>4778-270-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8509.01</v>
+        <v>4254.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4778-270-CM25</t>
+          <t>1233615-789-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4254.5</v>
+        <v>31908.78</v>
       </c>
     </row>
     <row r="84">
@@ -5909,7 +5909,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1233615-789-CM25</t>
+          <t>4778-238-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>31908.78</v>
+        <v>8509.01</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1113146-8-CM25</t>
+          <t>1746-76-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2235.4</v>
+        <v>2192.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1746-76-CM25</t>
+          <t>1113146-8-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2192.82</v>
+        <v>2235.4</v>
       </c>
     </row>
     <row r="88">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3791-591-CM25</t>
+          <t>817607-33-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5374.9</v>
+        <v>11832.3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>817607-33-CM25</t>
+          <t>697209-18-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6969,17 +6969,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>11832.3</v>
+        <v>2218.27</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>697209-18-CM25</t>
+          <t>3791-591-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2218.27</v>
+        <v>5374.9</v>
       </c>
     </row>
     <row r="103">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>854-186-CM25</t>
+          <t>854-187-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -7209,7 +7209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>854-187-CM25</t>
+          <t>2151-203-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7229,17 +7229,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7274,7 +7274,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2151-203-CM25</t>
+          <t>817607-34-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2200.46</v>
+        <v>3199.04</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>817607-34-CM25</t>
+          <t>854-186-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3199.04</v>
+        <v>2200.46</v>
       </c>
     </row>
     <row r="108">
@@ -7729,7 +7729,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1092-3192-CM25</t>
+          <t>1403-3889-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2256.44</v>
+        <v>6446.97</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1403-3889-CM25</t>
+          <t>1092-3192-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6446.97</v>
+        <v>2256.44</v>
       </c>
     </row>
     <row r="115">
@@ -8184,7 +8184,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>613-44-CM25</t>
+          <t>3791-722-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8204,17 +8204,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.836.000-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2212.79</v>
+        <v>5169.45</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3791-722-CM25</t>
+          <t>613-44-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8269,17 +8269,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.836.000-8</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5169.45</v>
+        <v>2212.79</v>
       </c>
     </row>
     <row r="122">
@@ -9809,7 +9809,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>4778-461-CM25</t>
+          <t>2151-294-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5194.75</v>
+        <v>2139.62</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2151-294-CM25</t>
+          <t>4778-461-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2139.62</v>
+        <v>5194.75</v>
       </c>
     </row>
     <row r="147">
@@ -10004,7 +10004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1608-152-CM25</t>
+          <t>3791-943-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2145.87</v>
+        <v>5163.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3791-943-CM25</t>
+          <t>1608-152-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -10128,7 +10128,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>5163.42</v>
+        <v>2145.87</v>
       </c>
     </row>
     <row r="150">
@@ -10329,7 +10329,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1692-2795-CM25</t>
+          <t>2042-284-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10349,17 +10349,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.253.400-k</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2591.8</v>
+        <v>9646.540000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2151-316-CM25</t>
+          <t>707426-147-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2154.25</v>
+        <v>5183.6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>707426-147-CM25</t>
+          <t>2151-316-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5183.6</v>
+        <v>2154.25</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2042-284-CM25</t>
+          <t>1692-2795-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10544,17 +10544,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.253.400-k</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Tortel</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>9646.540000000001</v>
+        <v>2591.8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4644-115-CM25</t>
+          <t>3797-604-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2171.51</v>
+        <v>5170.26</v>
       </c>
     </row>
     <row r="158">
@@ -10719,7 +10719,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3797-604-CM25</t>
+          <t>4644-115-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>5170.26</v>
+        <v>2171.51</v>
       </c>
     </row>
     <row r="160">
@@ -11239,7 +11239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>613-77-CM25</t>
+          <t>3791-1032-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.836.000-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3120</v>
+        <v>5199.99</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1403-4177-CM25</t>
+          <t>613-77-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.836.000-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>6239.99</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3791-1032-CM25</t>
+          <t>1403-4177-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>5199.99</v>
+        <v>6239.99</v>
       </c>
     </row>
     <row r="170">
@@ -11824,7 +11824,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3950-4555-CM25</t>
+          <t>3791-1103-CM25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11844,17 +11844,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3137.65</v>
+        <v>5229.41</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3791-1103-CM25</t>
+          <t>868-283-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5229.41</v>
+        <v>3974.35</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>868-283-CM25</t>
+          <t>3950-4555-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11974,17 +11974,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>3974.35</v>
+        <v>3137.65</v>
       </c>
     </row>
     <row r="179">
@@ -12799,7 +12799,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>657-187-CM25</t>
+          <t>1113144-113-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4464.05</v>
+        <v>5609.02</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1113144-113-CM25</t>
+          <t>657-187-CM25</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5609.02</v>
+        <v>4464.05</v>
       </c>
     </row>
     <row r="193">
@@ -13644,7 +13644,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>697209-43-CM25</t>
+          <t>2500-172-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13664,17 +13664,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>697209-44-CM25</t>
+          <t>697209-43-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13768,13 +13768,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2235.06</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2500-172-CM25</t>
+          <t>697209-44-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13794,17 +13794,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3192.95</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5038-66-CM25</t>
+          <t>3791-1290-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13859,17 +13859,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>3201.2</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1746-281-CM25</t>
+          <t>5038-66-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13924,17 +13924,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2240.84</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3791-1290-CM25</t>
+          <t>1746-281-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>5335.33</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4649-284-CM25</t>
+          <t>907-208-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2363.33</v>
+        <v>2721.7</v>
       </c>
     </row>
     <row r="211">
@@ -14164,7 +14164,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1092-3310-CM25</t>
+          <t>4649-284-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>7089.99</v>
+        <v>2363.33</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>907-208-CM25</t>
+          <t>1092-3310-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2721.7</v>
+        <v>7089.99</v>
       </c>
     </row>
     <row r="214">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>4609-601-CM25</t>
+          <t>3797-5103-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14424,7 +14424,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3797-5103-CM25</t>
+          <t>4609-601-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14449,12 +14449,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14944,7 +14944,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1692-3034-CM25</t>
+          <t>854-406-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14969,12 +14969,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -15003,13 +15003,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2287.3</v>
+        <v>4594.81</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>548870-76-CM25</t>
+          <t>1692-3034-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15029,17 +15029,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3283.21</v>
+        <v>2287.3</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>854-406-CM25</t>
+          <t>548870-76-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15094,17 +15094,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15133,7 +15133,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4594.81</v>
+        <v>3283.21</v>
       </c>
     </row>
     <row r="227">
@@ -16699,7 +16699,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2151-19-CM26</t>
+          <t>2151-21-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16764,7 +16764,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2151-21-CM26</t>
+          <t>2151-19-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16829,7 +16829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1746-9-CM26</t>
+          <t>1692-36-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2446.27</v>
+        <v>2912.23</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1692-36-CM26</t>
+          <t>1758-3-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>60.901.013-4</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2912.23</v>
+        <v>3378.18</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1758-3-CM26</t>
+          <t>1746-9-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>60.901.013-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,7 +17018,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3378.18</v>
+        <v>2446.27</v>
       </c>
     </row>
     <row r="256">
@@ -17479,7 +17479,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1195-80-CM26</t>
+          <t>2042-57-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17499,17 +17499,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.253.400-k</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,13 +17538,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>5528.43</v>
+        <v>5758.78</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2042-57-CM26</t>
+          <t>1195-80-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17564,17 +17564,17 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.253.400-k</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Tortel</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17603,7 +17603,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5758.78</v>
+        <v>5528.43</v>
       </c>
     </row>
     <row r="265">
@@ -17674,7 +17674,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1195-87-CM26</t>
+          <t>2182-19-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17694,17 +17694,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2421.78</v>
+        <v>2413.17</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2182-19-CM26</t>
+          <t>1195-87-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2413.17</v>
+        <v>2421.78</v>
       </c>
     </row>
     <row r="268">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>613-10-CM26</t>
+          <t>3540-166-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18279,17 +18279,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.836.000-8</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2967.23</v>
+        <v>2637.54</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3540-166-CM26</t>
+          <t>613-10-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.836.000-8</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2637.54</v>
+        <v>2967.23</v>
       </c>
     </row>
     <row r="277">
@@ -18454,7 +18454,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>4778-65-CM26</t>
+          <t>3791-253-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18479,12 +18479,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>10959.99</v>
+        <v>5031.94</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3791-253-CM26</t>
+          <t>4778-65-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5031.94</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2151-85-CM26</t>
+          <t>3797-218-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2277.7</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3797-218-CM26</t>
+          <t>2151-85-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>8690.74</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2151-83-CM26</t>
+          <t>2151-84-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18779,7 +18779,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2151-84-CM26</t>
+          <t>2151-83-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>4609-124-CM26</t>
+          <t>1746-39-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>3247.91</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="285">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1746-39-CM26</t>
+          <t>4609-124-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2273.54</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="287">
@@ -19169,7 +19169,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1403-189-CM26</t>
+          <t>5038-24-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19189,17 +19189,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2729.97</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="290">
@@ -19299,7 +19299,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>5038-24-CM26</t>
+          <t>1403-189-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19319,17 +19319,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,7 +19358,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>5459.95</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="292">
@@ -19689,7 +19689,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>4144-86-CM26</t>
+          <t>734-202-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19709,17 +19709,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>5615.9</v>
+        <v>28079.48</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>734-202-CM26</t>
+          <t>4144-86-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19774,17 +19774,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>28079.48</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="299">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>886182-114-CM26</t>
+          <t>3791-358-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19904,17 +19904,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7227.12</v>
+        <v>5559.32</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3791-358-CM26</t>
+          <t>886182-114-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19969,17 +19969,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5559.32</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="302">
@@ -20469,7 +20469,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>817607-14-CM26</t>
+          <t>4778-204-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,13 +20528,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>18924.59</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1746-91-CM26</t>
+          <t>4144-95-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20554,17 +20554,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2343.67</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2151-142-CM26</t>
+          <t>2151-141-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20664,7 +20664,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>4778-204-CM26</t>
+          <t>2151-142-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20689,12 +20689,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20723,13 +20723,13 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>11160.34</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4144-95-CM26</t>
+          <t>817607-14-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20749,17 +20749,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20788,13 +20788,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3348.1</v>
+        <v>18924.59</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2151-141-CM26</t>
+          <t>1746-91-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20853,7 +20853,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3348.1</v>
+        <v>2343.67</v>
       </c>
     </row>
     <row r="315">
@@ -21704,7 +21704,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1692-352-CM26</t>
+          <t>4778-260-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21729,12 +21729,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21763,13 +21763,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3889.49</v>
+        <v>11112.84</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>4778-260-CM26</t>
+          <t>1692-352-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>11112.84</v>
+        <v>3889.49</v>
       </c>
     </row>
     <row r="330">
@@ -22679,7 +22679,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3791-722-CM26</t>
+          <t>1403-454-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>6972.59</v>
+        <v>3395.74</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1403-454-CM26</t>
+          <t>3791-722-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22769,12 +22769,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3395.74</v>
+        <v>6972.59</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1195-366-CM26</t>
+          <t>3791-730-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22868,13 +22868,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>4458.36</v>
+        <v>6687.55</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>3791-730-CM26</t>
+          <t>1195-366-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22933,7 +22933,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6687.55</v>
+        <v>4458.36</v>
       </c>
     </row>
     <row r="347">
@@ -24499,7 +24499,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1415-34-CM26</t>
+          <t>4609-321-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24524,12 +24524,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>60.511.111-4</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24558,13 +24558,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2297.5</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>4609-321-CM26</t>
+          <t>1415-34-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24589,12 +24589,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.511.111-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24623,7 +24623,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3206.6</v>
+        <v>2297.5</v>
       </c>
     </row>
     <row r="373">
@@ -24694,7 +24694,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3791-884-CM26</t>
+          <t>1286987-25-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24714,17 +24714,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>5990.61</v>
+        <v>2876.36</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1286987-25-CM26</t>
+          <t>3791-884-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24779,17 +24779,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>65.797.310-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,7 +24818,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2876.36</v>
+        <v>5990.61</v>
       </c>
     </row>
     <row r="376">
@@ -25019,7 +25019,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2151-301-CM26</t>
+          <t>3791-927-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -25039,17 +25039,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -25078,13 +25078,13 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2352.08</v>
+        <v>6565.56</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>3791-927-CM26</t>
+          <t>2151-301-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25104,17 +25104,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -25143,7 +25143,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>6565.56</v>
+        <v>2352.08</v>
       </c>
     </row>
     <row r="381">
@@ -25214,7 +25214,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1403-649-CM26</t>
+          <t>3791-946-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25234,17 +25234,17 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25273,13 +25273,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>2357.46</v>
+        <v>6065.79</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>3791-946-CM26</t>
+          <t>1403-649-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25299,17 +25299,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25338,7 +25338,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>6065.79</v>
+        <v>2357.46</v>
       </c>
     </row>
     <row r="384">
@@ -26059,7 +26059,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1403-707-CM26</t>
+          <t>1195-471-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26118,13 +26118,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2678.38</v>
+        <v>6428.11</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1195-471-CM26</t>
+          <t>1403-707-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26183,7 +26183,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>6428.11</v>
+        <v>2678.38</v>
       </c>
     </row>
     <row r="397">
@@ -26319,7 +26319,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>4644-73-CM26</t>
+          <t>3791-1084-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26339,17 +26339,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,7 +26378,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3188.4</v>
+        <v>6376.81</v>
       </c>
     </row>
     <row r="400">
@@ -26449,7 +26449,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>3791-1084-CM26</t>
+          <t>4644-73-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26469,17 +26469,17 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26508,7 +26508,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>6376.81</v>
+        <v>3188.4</v>
       </c>
     </row>
     <row r="402">
@@ -26644,7 +26644,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1746-256-CM26</t>
+          <t>4140-65-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26664,17 +26664,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26703,13 +26703,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>3151.26</v>
+        <v>5252.1</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>4140-65-CM26</t>
+          <t>1746-256-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26729,17 +26729,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26768,7 +26768,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>5252.1</v>
+        <v>3151.26</v>
       </c>
     </row>
     <row r="406">
@@ -26839,7 +26839,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2500-147-CM26</t>
+          <t>3797-673-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26854,22 +26854,22 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26898,13 +26898,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>5177.54</v>
+        <v>10423.29</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>817607-53-CM26</t>
+          <t>2500-147-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -26929,12 +26929,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,13 +26963,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>6223.42</v>
+        <v>5177.54</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1692-687-CM26</t>
+          <t>817607-53-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -26994,12 +26994,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>5156.23</v>
+        <v>6223.42</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>3540-597-CM26</t>
+          <t>1692-687-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2371.87</v>
+        <v>5156.23</v>
       </c>
     </row>
     <row r="411">
@@ -27164,66 +27164,1301 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
+          <t>3540-597-CM26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>61.101.037-0</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="n">
+        <v>2371.87</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
           <t>1173807-8-CM26</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>2239-13-LR25</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
+      <c r="D413" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
         <is>
           <t>70.816.700-2</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
+      <c r="G413" t="inlineStr">
         <is>
           <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J412" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K412" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L412" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M412" s="2" t="n">
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="n">
         <v>2236.05</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>3791-1152-CM26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="n">
+        <v>6859.96</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2500-159-CM26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="n">
+        <v>6139.68</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>591248-23-CM26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>70.816.700-2</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="n">
+        <v>2251.22</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>817607-57-CM26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M417" s="2" t="n">
+        <v>15755.44</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>1458-23-CM26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>60.103.003-9</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M418" s="2" t="n">
+        <v>2236.57</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>734-739-CM26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>30616.93</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>3540-611-CM26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>61.101.037-0</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>2852.46</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>1405-57-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>60.511.113-0</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CAPITÁN PRAT</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>2954.33</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1905-87-CM26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>61.002.027-5</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>8174.86</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>1403-797-CM26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>61.004.101-9</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>5109.29</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1233615-1806-CM26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>15327.86</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>3791-1207-CM26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>6646.2</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>3791-1213-CM26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>6097</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2151-408-CM26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>2211.95</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2151-409-CM26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>2211.95</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4609-498-CM26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>10237.3</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>3791-1247-CM26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>2221.49</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>4609-499-CM26</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>3071.19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
+++ b/docs/oc-regiones/suministro-de-combustibles/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M433"/>
+  <dimension ref="A1:M435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9874,7 +9874,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2151-294-CM25</t>
+          <t>4778-461-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2139.62</v>
+        <v>5194.75</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4778-461-CM25</t>
+          <t>2151-294-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5194.75</v>
+        <v>2139.62</v>
       </c>
     </row>
     <row r="148">
@@ -17999,7 +17999,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>734-77-CM26</t>
+          <t>734-78-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>6885.39</v>
+        <v>34426.96</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>734-78-CM26</t>
+          <t>734-77-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>34426.96</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="273">
@@ -18519,7 +18519,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3791-253-CM26</t>
+          <t>4778-65-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,13 +18578,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>5031.94</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4778-65-CM26</t>
+          <t>3791-253-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18609,12 +18609,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>10959.99</v>
+        <v>5031.94</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3797-218-CM26</t>
+          <t>2151-85-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>8690.74</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2151-85-CM26</t>
+          <t>2151-83-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18779,7 +18779,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2151-84-CM26</t>
+          <t>3797-218-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2277.7</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2151-83-CM26</t>
+          <t>2151-84-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18909,7 +18909,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1746-39-CM26</t>
+          <t>4609-124-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,7 +18968,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2273.54</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="286">
@@ -19039,7 +19039,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>4609-124-CM26</t>
+          <t>1746-39-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3247.91</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="288">
@@ -19234,7 +19234,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>5038-24-CM26</t>
+          <t>1403-189-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19254,17 +19254,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,7 +19293,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>5459.95</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="291">
@@ -19364,7 +19364,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1403-189-CM26</t>
+          <t>5038-24-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19384,17 +19384,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2729.97</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="293">
@@ -19754,7 +19754,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>734-202-CM26</t>
+          <t>4144-86-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19774,17 +19774,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19813,13 +19813,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>28079.48</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>4144-86-CM26</t>
+          <t>734-202-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19839,17 +19839,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5615.9</v>
+        <v>28079.48</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>886182-114-CM26</t>
+          <t>1403-260-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19904,17 +19904,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7227.12</v>
+        <v>2779.66</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1403-260-CM26</t>
+          <t>886182-114-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19969,17 +19969,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2779.66</v>
+        <v>7227.12</v>
       </c>
     </row>
     <row r="302">
@@ -20079,7 +20079,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3791-376-CM26</t>
+          <t>4852-6-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>7940.5</v>
+        <v>4514.21</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>4852-6-CM26</t>
+          <t>3791-376-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,7 +20203,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>4514.21</v>
+        <v>7940.5</v>
       </c>
     </row>
     <row r="305">
@@ -20274,7 +20274,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3791-417-CM26</t>
+          <t>854-60-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>6742.56</v>
+        <v>5618.8</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>854-60-CM26</t>
+          <t>3791-417-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>5618.8</v>
+        <v>6742.56</v>
       </c>
     </row>
     <row r="308">
@@ -20534,7 +20534,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2151-141-CM26</t>
+          <t>4778-204-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,13 +20593,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3348.1</v>
+        <v>11160.34</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>817607-14-CM26</t>
+          <t>4144-95-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20619,17 +20619,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20658,7 +20658,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>18924.59</v>
+        <v>3348.1</v>
       </c>
     </row>
     <row r="312">
@@ -20794,7 +20794,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>4778-204-CM26</t>
+          <t>817607-14-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>11160.34</v>
+        <v>18924.59</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4144-95-CM26</t>
+          <t>2151-141-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20879,17 +20879,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.253.000-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -22289,7 +22289,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>3791-657-CM26</t>
+          <t>1233615-887-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>7406.99</v>
+        <v>50319.25</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1233615-887-CM26</t>
+          <t>3791-657-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,7 +22413,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>50319.25</v>
+        <v>7406.99</v>
       </c>
     </row>
     <row r="339">
@@ -23719,7 +23719,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>3797-489-CM26</t>
+          <t>3797-488-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>7535.06</v>
+        <v>2314.34</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>3797-488-CM26</t>
+          <t>3797-489-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23843,13 +23843,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2314.34</v>
+        <v>7535.06</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1113144-27-CM26</t>
+          <t>1113146-13-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23908,7 +23908,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3229.84</v>
+        <v>5383.06</v>
       </c>
     </row>
     <row r="362">
@@ -23979,7 +23979,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1113146-13-CM26</t>
+          <t>1113144-27-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24038,7 +24038,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>5383.06</v>
+        <v>3229.84</v>
       </c>
     </row>
     <row r="364">
@@ -24564,7 +24564,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>4609-321-CM26</t>
+          <t>1415-34-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24589,12 +24589,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.511.111-4</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24623,13 +24623,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>3206.6</v>
+        <v>2297.5</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1415-34-CM26</t>
+          <t>3950-1153-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24654,12 +24654,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>60.511.111-4</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24688,13 +24688,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2297.5</v>
+        <v>16033.01</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3950-1153-CM26</t>
+          <t>4609-321-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24719,12 +24719,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>16033.01</v>
+        <v>3206.6</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1286987-25-CM26</t>
+          <t>3791-884-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24779,17 +24779,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>65.797.310-6</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,13 +24818,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2876.36</v>
+        <v>5990.61</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>3791-884-CM26</t>
+          <t>1286987-25-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24844,17 +24844,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24883,7 +24883,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>5990.61</v>
+        <v>2876.36</v>
       </c>
     </row>
     <row r="377">
@@ -25929,7 +25929,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1692-592-CM26</t>
+          <t>4609-400-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5444.13</v>
+        <v>10888.26</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>4609-400-CM26</t>
+          <t>1692-592-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>10888.26</v>
+        <v>5444.13</v>
       </c>
     </row>
     <row r="395">
@@ -27164,7 +27164,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1692-687-CM26</t>
+          <t>907-154-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27184,17 +27184,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27223,13 +27223,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>5156.23</v>
+        <v>20624.94</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>907-154-CM26</t>
+          <t>1692-687-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27249,17 +27249,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,7 +27288,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>20624.94</v>
+        <v>5156.23</v>
       </c>
     </row>
     <row r="414">
@@ -28009,7 +28009,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1403-797-CM26</t>
+          <t>1233615-1806-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28029,17 +28029,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>5109.29</v>
+        <v>15327.86</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1233615-1806-CM26</t>
+          <t>1403-797-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28099,12 +28099,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -28133,7 +28133,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>15327.86</v>
+        <v>5109.29</v>
       </c>
     </row>
     <row r="427">
@@ -28399,7 +28399,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>4609-498-CM26</t>
+          <t>3791-1247-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28424,12 +28424,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28458,13 +28458,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>10237.3</v>
+        <v>2221.49</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>3791-1247-CM26</t>
+          <t>4609-498-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28523,7 +28523,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2221.49</v>
+        <v>10237.3</v>
       </c>
     </row>
     <row r="433">
@@ -28589,6 +28589,136 @@
       </c>
       <c r="M433" s="2" t="n">
         <v>3071.19</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>3797-781-CM26</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>4257.13</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1195-548-CM26</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="n">
+        <v>14190.44</v>
       </c>
     </row>
   </sheetData>
